--- a/data/trans_orig/MCS12_SP_R2-Clase-trans_orig.xlsx
+++ b/data/trans_orig/MCS12_SP_R2-Clase-trans_orig.xlsx
@@ -538,7 +538,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población por debajo de la mediana (53.5790) de la puntuación del componente de salud mental (SF12) en 2007</t>
+          <t>Población por debajo de la mediana (53.579) de la puntuación del componente de salud mental (SF12) en 2007 (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -733,12 +733,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>171310</t>
+          <t>172020</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>215330</t>
+          <t>215718</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -748,12 +748,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>36,16%</t>
+          <t>36,31%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>45,45%</t>
+          <t>45,53%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -768,12 +768,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>138923</t>
+          <t>139992</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>173276</t>
+          <t>172871</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -783,12 +783,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>45,3%</t>
+          <t>45,65%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>56,5%</t>
+          <t>56,37%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -803,12 +803,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>319913</t>
+          <t>319666</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>377087</t>
+          <t>376275</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -818,12 +818,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>40,99%</t>
+          <t>40,96%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>48,32%</t>
+          <t>48,21%</t>
         </is>
       </c>
     </row>
@@ -846,12 +846,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>258446</t>
+          <t>258058</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>302466</t>
+          <t>301756</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -861,12 +861,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>54,55%</t>
+          <t>54,47%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>63,84%</t>
+          <t>63,69%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -881,12 +881,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>133404</t>
+          <t>133809</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>167757</t>
+          <t>166688</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -896,12 +896,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>43,5%</t>
+          <t>43,63%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>54,7%</t>
+          <t>54,35%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -916,12 +916,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>403370</t>
+          <t>404182</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>460544</t>
+          <t>460791</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -931,12 +931,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>51,68%</t>
+          <t>51,79%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>59,01%</t>
+          <t>59,04%</t>
         </is>
       </c>
     </row>
@@ -1076,12 +1076,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>123654</t>
+          <t>124975</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>161599</t>
+          <t>162708</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1091,12 +1091,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>33,7%</t>
+          <t>34,06%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>44,04%</t>
+          <t>44,34%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1111,12 +1111,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>184767</t>
+          <t>186274</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>223974</t>
+          <t>225216</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1126,12 +1126,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>49,69%</t>
+          <t>50,09%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>60,23%</t>
+          <t>60,56%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1146,12 +1146,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>318256</t>
+          <t>319936</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>373322</t>
+          <t>375873</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1161,12 +1161,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>43,08%</t>
+          <t>43,3%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>50,53%</t>
+          <t>50,88%</t>
         </is>
       </c>
     </row>
@@ -1189,12 +1189,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>205335</t>
+          <t>204226</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>243280</t>
+          <t>241959</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1204,12 +1204,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>55,96%</t>
+          <t>55,66%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>66,3%</t>
+          <t>65,94%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1224,12 +1224,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>147891</t>
+          <t>146649</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>187098</t>
+          <t>185591</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1239,12 +1239,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>39,77%</t>
+          <t>39,44%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>50,31%</t>
+          <t>49,91%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1259,12 +1259,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>365477</t>
+          <t>362926</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>420543</t>
+          <t>418863</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1274,12 +1274,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>49,47%</t>
+          <t>49,12%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>56,92%</t>
+          <t>56,7%</t>
         </is>
       </c>
     </row>
@@ -1419,12 +1419,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>217942</t>
+          <t>221154</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>265284</t>
+          <t>264703</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1434,12 +1434,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>40,18%</t>
+          <t>40,77%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>48,91%</t>
+          <t>48,8%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1454,12 +1454,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>82337</t>
+          <t>83374</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>108954</t>
+          <t>108198</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1469,12 +1469,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>49,07%</t>
+          <t>49,69%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>64,94%</t>
+          <t>64,49%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1489,12 +1489,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>311962</t>
+          <t>314274</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>364732</t>
+          <t>363911</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1504,12 +1504,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>43,93%</t>
+          <t>44,25%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>51,36%</t>
+          <t>51,24%</t>
         </is>
       </c>
     </row>
@@ -1532,12 +1532,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>277105</t>
+          <t>277686</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>324447</t>
+          <t>321235</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1547,12 +1547,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>51,09%</t>
+          <t>51,2%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>59,82%</t>
+          <t>59,23%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1567,12 +1567,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>58828</t>
+          <t>59584</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>85445</t>
+          <t>84408</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1582,12 +1582,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>35,06%</t>
+          <t>35,51%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>50,93%</t>
+          <t>50,31%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1602,12 +1602,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>345439</t>
+          <t>346260</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>398209</t>
+          <t>395897</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1617,12 +1617,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>48,64%</t>
+          <t>48,76%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>56,07%</t>
+          <t>55,75%</t>
         </is>
       </c>
     </row>
@@ -1762,12 +1762,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>561358</t>
+          <t>560805</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>631030</t>
+          <t>629229</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1777,12 +1777,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>45,33%</t>
+          <t>45,29%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>50,96%</t>
+          <t>50,81%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1797,12 +1797,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>352558</t>
+          <t>354041</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>409617</t>
+          <t>411050</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1812,12 +1812,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>49,36%</t>
+          <t>49,57%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>57,35%</t>
+          <t>57,55%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1832,12 +1832,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>937319</t>
+          <t>937270</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>1026069</t>
+          <t>1026198</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1875,12 +1875,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>607304</t>
+          <t>609105</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>676976</t>
+          <t>677529</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1890,12 +1890,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>49,04%</t>
+          <t>49,19%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>54,67%</t>
+          <t>54,71%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1910,12 +1910,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>304668</t>
+          <t>303235</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>361727</t>
+          <t>360244</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1925,12 +1925,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>42,65%</t>
+          <t>42,45%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>50,64%</t>
+          <t>50,43%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1945,12 +1945,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>926551</t>
+          <t>926422</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1015301</t>
+          <t>1015350</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -2105,12 +2105,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>132811</t>
+          <t>130915</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>170576</t>
+          <t>170269</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2120,12 +2120,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>37,89%</t>
+          <t>37,35%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>48,66%</t>
+          <t>48,57%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2140,12 +2140,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>308230</t>
+          <t>308518</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>356458</t>
+          <t>357102</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2155,12 +2155,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>54,19%</t>
+          <t>54,24%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>62,67%</t>
+          <t>62,79%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2175,12 +2175,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>454541</t>
+          <t>452046</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>513940</t>
+          <t>512003</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2190,12 +2190,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>49,44%</t>
+          <t>49,17%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>55,91%</t>
+          <t>55,69%</t>
         </is>
       </c>
     </row>
@@ -2218,12 +2218,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>179979</t>
+          <t>180286</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>217744</t>
+          <t>219640</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2233,12 +2233,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>51,34%</t>
+          <t>51,43%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>62,11%</t>
+          <t>62,65%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2253,12 +2253,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>212294</t>
+          <t>211650</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>260522</t>
+          <t>260234</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2268,12 +2268,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>37,33%</t>
+          <t>37,21%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>45,81%</t>
+          <t>45,76%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2288,12 +2288,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>405367</t>
+          <t>407304</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>464766</t>
+          <t>467261</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2303,12 +2303,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>44,09%</t>
+          <t>44,31%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>50,56%</t>
+          <t>50,83%</t>
         </is>
       </c>
     </row>
@@ -2448,12 +2448,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>68976</t>
+          <t>70506</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>100791</t>
+          <t>101439</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -2463,12 +2463,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>23,13%</t>
+          <t>23,64%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>33,8%</t>
+          <t>34,02%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2483,12 +2483,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>621916</t>
+          <t>625518</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>694243</t>
+          <t>694322</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -2498,12 +2498,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>49,8%</t>
+          <t>50,09%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>55,59%</t>
+          <t>55,6%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2518,12 +2518,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>704927</t>
+          <t>707950</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>783761</t>
+          <t>783959</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -2533,12 +2533,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>45,57%</t>
+          <t>45,76%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>50,66%</t>
+          <t>50,68%</t>
         </is>
       </c>
     </row>
@@ -2561,12 +2561,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>197410</t>
+          <t>196762</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>229225</t>
+          <t>227695</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2576,12 +2576,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>66,2%</t>
+          <t>65,98%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>76,87%</t>
+          <t>76,36%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2596,12 +2596,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>554517</t>
+          <t>554438</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>626844</t>
+          <t>623242</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2611,12 +2611,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>44,41%</t>
+          <t>44,4%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>50,2%</t>
+          <t>49,91%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2631,12 +2631,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>763199</t>
+          <t>763001</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>842033</t>
+          <t>839010</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2646,12 +2646,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>49,34%</t>
+          <t>49,32%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>54,43%</t>
+          <t>54,24%</t>
         </is>
       </c>
     </row>
@@ -2791,12 +2791,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>1359187</t>
+          <t>1358481</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>1471585</t>
+          <t>1471031</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2806,12 +2806,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>41,56%</t>
+          <t>41,54%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>45,0%</t>
+          <t>44,98%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2826,12 +2826,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>1772605</t>
+          <t>1772265</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>1889024</t>
+          <t>1889033</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2841,7 +2841,7 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>52,47%</t>
+          <t>52,46%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
@@ -2861,12 +2861,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>3160800</t>
+          <t>3170890</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>3325063</t>
+          <t>3326348</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2876,12 +2876,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>47,54%</t>
+          <t>47,69%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>50,01%</t>
+          <t>50,03%</t>
         </is>
       </c>
     </row>
@@ -2904,12 +2904,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>1798605</t>
+          <t>1799159</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>1911003</t>
+          <t>1911709</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -2919,12 +2919,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>55,0%</t>
+          <t>55,02%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>58,44%</t>
+          <t>58,46%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -2939,12 +2939,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>1489100</t>
+          <t>1489091</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>1605519</t>
+          <t>1605859</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -2959,7 +2959,7 @@
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>47,53%</t>
+          <t>47,54%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -2974,12 +2974,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>3323251</t>
+          <t>3321966</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>3487514</t>
+          <t>3477424</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -2989,12 +2989,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>49,99%</t>
+          <t>49,97%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>52,46%</t>
+          <t>52,31%</t>
         </is>
       </c>
     </row>
@@ -3173,7 +3173,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población por debajo de la mediana (53.5790) de la puntuación del componente de salud mental (SF12) en 2012</t>
+          <t>Población por debajo de la mediana (53.579) de la puntuación del componente de salud mental (SF12) en 2012 (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -3368,12 +3368,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>200213</t>
+          <t>198660</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>244018</t>
+          <t>243520</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -3383,12 +3383,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>45,79%</t>
+          <t>45,44%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>55,81%</t>
+          <t>55,7%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -3403,12 +3403,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>157930</t>
+          <t>157319</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>195224</t>
+          <t>195472</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -3418,12 +3418,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>50,22%</t>
+          <t>50,03%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>62,08%</t>
+          <t>62,16%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -3438,12 +3438,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>370318</t>
+          <t>372897</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>427265</t>
+          <t>430433</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -3453,12 +3453,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>49,27%</t>
+          <t>49,61%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>56,84%</t>
+          <t>57,26%</t>
         </is>
       </c>
     </row>
@@ -3481,12 +3481,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>193193</t>
+          <t>193691</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>236998</t>
+          <t>238551</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -3496,12 +3496,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>44,19%</t>
+          <t>44,3%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>54,21%</t>
+          <t>54,56%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -3516,12 +3516,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>119230</t>
+          <t>118982</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>156524</t>
+          <t>157135</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -3531,12 +3531,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>37,92%</t>
+          <t>37,84%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>49,78%</t>
+          <t>49,97%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -3551,12 +3551,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>324400</t>
+          <t>321232</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>381347</t>
+          <t>378768</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -3566,12 +3566,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>43,16%</t>
+          <t>42,74%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>50,73%</t>
+          <t>50,39%</t>
         </is>
       </c>
     </row>
@@ -3711,12 +3711,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>181450</t>
+          <t>180398</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>224232</t>
+          <t>223522</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -3726,12 +3726,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>43,33%</t>
+          <t>43,08%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>53,54%</t>
+          <t>53,37%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -3746,12 +3746,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>196610</t>
+          <t>197902</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>235975</t>
+          <t>235750</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -3761,12 +3761,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>58,17%</t>
+          <t>58,55%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>69,81%</t>
+          <t>69,75%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -3781,12 +3781,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>392570</t>
+          <t>390032</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>452409</t>
+          <t>447447</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -3796,12 +3796,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>51,87%</t>
+          <t>51,54%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>59,78%</t>
+          <t>59,12%</t>
         </is>
       </c>
     </row>
@@ -3824,12 +3824,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>194565</t>
+          <t>195275</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>237347</t>
+          <t>238399</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -3839,12 +3839,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>46,46%</t>
+          <t>46,63%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>56,67%</t>
+          <t>56,92%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -3859,12 +3859,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>102036</t>
+          <t>102261</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>141401</t>
+          <t>140109</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -3874,12 +3874,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>30,19%</t>
+          <t>30,25%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>41,83%</t>
+          <t>41,45%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -3894,12 +3894,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>304399</t>
+          <t>309361</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>364238</t>
+          <t>366776</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -3909,12 +3909,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>40,22%</t>
+          <t>40,88%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>48,13%</t>
+          <t>48,46%</t>
         </is>
       </c>
     </row>
@@ -4054,12 +4054,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>310012</t>
+          <t>306322</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>360700</t>
+          <t>359513</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -4069,12 +4069,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>49,25%</t>
+          <t>48,67%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>57,31%</t>
+          <t>57,12%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -4089,12 +4089,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>155478</t>
+          <t>155336</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>186996</t>
+          <t>186897</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -4104,12 +4104,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>59,77%</t>
+          <t>59,71%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>71,89%</t>
+          <t>71,85%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -4124,12 +4124,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>474348</t>
+          <t>473510</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>537268</t>
+          <t>536656</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -4139,12 +4139,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>53,32%</t>
+          <t>53,23%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>60,4%</t>
+          <t>60,33%</t>
         </is>
       </c>
     </row>
@@ -4167,12 +4167,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>268715</t>
+          <t>269902</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>319403</t>
+          <t>323093</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -4182,12 +4182,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>42,69%</t>
+          <t>42,88%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>50,75%</t>
+          <t>51,33%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -4202,12 +4202,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>73133</t>
+          <t>73232</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>104651</t>
+          <t>104793</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -4217,12 +4217,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>28,11%</t>
+          <t>28,15%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>40,23%</t>
+          <t>40,29%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -4237,12 +4237,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>352276</t>
+          <t>352888</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>415196</t>
+          <t>416034</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -4252,12 +4252,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>39,6%</t>
+          <t>39,67%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>46,68%</t>
+          <t>46,77%</t>
         </is>
       </c>
     </row>
@@ -4397,12 +4397,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>555998</t>
+          <t>559184</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>631817</t>
+          <t>631598</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -4412,12 +4412,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>47,97%</t>
+          <t>48,25%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>54,51%</t>
+          <t>54,49%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -4432,12 +4432,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>442370</t>
+          <t>435318</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>498940</t>
+          <t>493694</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -4447,12 +4447,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>57,7%</t>
+          <t>56,78%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>65,08%</t>
+          <t>64,4%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -4467,12 +4467,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>1014420</t>
+          <t>1019743</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>1105230</t>
+          <t>1108702</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -4482,12 +4482,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>52,68%</t>
+          <t>52,96%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>57,39%</t>
+          <t>57,57%</t>
         </is>
       </c>
     </row>
@@ -4510,12 +4510,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>527192</t>
+          <t>527411</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>603011</t>
+          <t>599825</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -4525,12 +4525,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>45,49%</t>
+          <t>45,51%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>52,03%</t>
+          <t>51,75%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -4545,12 +4545,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>267717</t>
+          <t>272963</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>324287</t>
+          <t>331339</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -4560,12 +4560,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>34,92%</t>
+          <t>35,6%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>42,3%</t>
+          <t>43,22%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -4580,12 +4580,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>820437</t>
+          <t>816965</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>911247</t>
+          <t>905924</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -4595,12 +4595,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>42,61%</t>
+          <t>42,43%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>47,32%</t>
+          <t>47,04%</t>
         </is>
       </c>
     </row>
@@ -4740,12 +4740,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>213549</t>
+          <t>214914</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>260915</t>
+          <t>261379</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -4755,12 +4755,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>41,82%</t>
+          <t>42,09%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>51,1%</t>
+          <t>51,19%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -4775,12 +4775,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>465941</t>
+          <t>465943</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>521622</t>
+          <t>517920</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -4795,7 +4795,7 @@
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>68,5%</t>
+          <t>68,01%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -4810,12 +4810,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>695142</t>
+          <t>697606</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>765832</t>
+          <t>768597</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -4825,12 +4825,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>54,64%</t>
+          <t>54,84%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>60,2%</t>
+          <t>60,42%</t>
         </is>
       </c>
     </row>
@@ -4853,12 +4853,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>249681</t>
+          <t>249217</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>297047</t>
+          <t>295682</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -4868,12 +4868,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>48,9%</t>
+          <t>48,81%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>58,18%</t>
+          <t>57,91%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -4888,12 +4888,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>239900</t>
+          <t>243602</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>295581</t>
+          <t>295579</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -4903,7 +4903,7 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>31,5%</t>
+          <t>31,99%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
@@ -4923,12 +4923,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>506286</t>
+          <t>503521</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>576976</t>
+          <t>574512</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -4938,12 +4938,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>39,8%</t>
+          <t>39,58%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>45,36%</t>
+          <t>45,16%</t>
         </is>
       </c>
     </row>
@@ -5083,12 +5083,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>71137</t>
+          <t>71178</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>100870</t>
+          <t>102671</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -5098,12 +5098,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>26,65%</t>
+          <t>26,67%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>37,8%</t>
+          <t>38,47%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -5118,12 +5118,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>637654</t>
+          <t>636342</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>703925</t>
+          <t>702602</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -5133,12 +5133,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>57,48%</t>
+          <t>57,36%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>63,45%</t>
+          <t>63,33%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -5153,12 +5153,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>717904</t>
+          <t>718721</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>793777</t>
+          <t>794843</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -5168,12 +5168,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>52,16%</t>
+          <t>52,22%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>57,68%</t>
+          <t>57,75%</t>
         </is>
       </c>
     </row>
@@ -5196,12 +5196,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>166012</t>
+          <t>164211</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>195745</t>
+          <t>195704</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -5211,12 +5211,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>62,2%</t>
+          <t>61,53%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>73,35%</t>
+          <t>73,33%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -5231,12 +5231,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>405426</t>
+          <t>406749</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>471697</t>
+          <t>473009</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -5246,12 +5246,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>36,55%</t>
+          <t>36,67%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>42,52%</t>
+          <t>42,64%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -5266,12 +5266,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>582456</t>
+          <t>581390</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>658329</t>
+          <t>657512</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -5281,12 +5281,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>42,32%</t>
+          <t>42,25%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>47,84%</t>
+          <t>47,78%</t>
         </is>
       </c>
     </row>
@@ -5426,12 +5426,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>1616859</t>
+          <t>1624206</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>1735751</t>
+          <t>1738806</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -5441,12 +5441,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>47,25%</t>
+          <t>47,46%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>50,72%</t>
+          <t>50,81%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -5461,12 +5461,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>2140915</t>
+          <t>2135351</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>2260604</t>
+          <t>2257824</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -5476,12 +5476,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>60,31%</t>
+          <t>60,15%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>63,68%</t>
+          <t>63,6%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -5496,12 +5496,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>3785816</t>
+          <t>3782405</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>3951832</t>
+          <t>3961541</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -5511,12 +5511,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>54,3%</t>
+          <t>54,25%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>56,68%</t>
+          <t>56,82%</t>
         </is>
       </c>
     </row>
@@ -5539,12 +5539,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>1686159</t>
+          <t>1683104</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>1805051</t>
+          <t>1797704</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -5554,12 +5554,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>49,28%</t>
+          <t>49,19%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>52,75%</t>
+          <t>52,54%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -5574,12 +5574,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>1289521</t>
+          <t>1292301</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>1409210</t>
+          <t>1414774</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -5589,12 +5589,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>36,32%</t>
+          <t>36,4%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>39,69%</t>
+          <t>39,85%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -5609,12 +5609,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>3020203</t>
+          <t>3010494</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>3186219</t>
+          <t>3189630</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -5624,12 +5624,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>43,32%</t>
+          <t>43,18%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>45,7%</t>
+          <t>45,75%</t>
         </is>
       </c>
     </row>
@@ -5808,7 +5808,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población por debajo de la mediana (53.5790) de la puntuación del componente de salud mental (SF12) en 2016</t>
+          <t>Población por debajo de la mediana (53.579) de la puntuación del componente de salud mental (SF12) en 2016 (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -6003,12 +6003,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>184085</t>
+          <t>181553</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>224386</t>
+          <t>225817</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -6018,12 +6018,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>42,9%</t>
+          <t>42,31%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>52,29%</t>
+          <t>52,63%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -6038,12 +6038,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>148968</t>
+          <t>147978</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>188226</t>
+          <t>186190</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -6053,12 +6053,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>42,92%</t>
+          <t>42,64%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>54,24%</t>
+          <t>53,65%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -6073,12 +6073,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>344721</t>
+          <t>345409</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>400407</t>
+          <t>401286</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -6088,12 +6088,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>44,41%</t>
+          <t>44,5%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>51,59%</t>
+          <t>51,7%</t>
         </is>
       </c>
     </row>
@@ -6116,12 +6116,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>204706</t>
+          <t>203275</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>245007</t>
+          <t>247539</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -6131,12 +6131,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>47,71%</t>
+          <t>47,37%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>57,1%</t>
+          <t>57,69%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -6151,12 +6151,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>158829</t>
+          <t>160865</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>198087</t>
+          <t>199077</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -6166,12 +6166,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>45,76%</t>
+          <t>46,35%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>57,08%</t>
+          <t>57,36%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -6186,12 +6186,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>375740</t>
+          <t>374861</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>431426</t>
+          <t>430738</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -6201,12 +6201,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>48,41%</t>
+          <t>48,3%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>55,59%</t>
+          <t>55,5%</t>
         </is>
       </c>
     </row>
@@ -6346,12 +6346,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>154791</t>
+          <t>155381</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>195775</t>
+          <t>193907</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -6361,12 +6361,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>41,03%</t>
+          <t>41,19%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>51,9%</t>
+          <t>51,4%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -6381,12 +6381,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>178646</t>
+          <t>178043</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>216477</t>
+          <t>217626</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -6396,12 +6396,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>47,99%</t>
+          <t>47,83%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>58,15%</t>
+          <t>58,46%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -6416,12 +6416,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>347145</t>
+          <t>345815</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>401320</t>
+          <t>401136</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -6431,12 +6431,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>46,32%</t>
+          <t>46,14%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>53,55%</t>
+          <t>53,52%</t>
         </is>
       </c>
     </row>
@@ -6459,12 +6459,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>181452</t>
+          <t>183320</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>222436</t>
+          <t>221846</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -6474,12 +6474,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>48,1%</t>
+          <t>48,6%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>58,97%</t>
+          <t>58,81%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -6494,12 +6494,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>155796</t>
+          <t>154647</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>193627</t>
+          <t>194230</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -6509,12 +6509,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>41,85%</t>
+          <t>41,54%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>52,01%</t>
+          <t>52,17%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -6529,12 +6529,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>348180</t>
+          <t>348364</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>402355</t>
+          <t>403685</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -6544,12 +6544,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>46,45%</t>
+          <t>46,48%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>53,68%</t>
+          <t>53,86%</t>
         </is>
       </c>
     </row>
@@ -6689,12 +6689,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>242207</t>
+          <t>243169</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>289357</t>
+          <t>286879</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -6704,12 +6704,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>46,41%</t>
+          <t>46,59%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>55,44%</t>
+          <t>54,97%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -6724,12 +6724,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>86533</t>
+          <t>85467</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>113958</t>
+          <t>113290</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -6739,12 +6739,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>52,09%</t>
+          <t>51,45%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>68,6%</t>
+          <t>68,2%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -6759,12 +6759,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>336980</t>
+          <t>337578</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>390468</t>
+          <t>392133</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -6774,12 +6774,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>48,98%</t>
+          <t>49,06%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>56,75%</t>
+          <t>56,99%</t>
         </is>
       </c>
     </row>
@@ -6802,12 +6802,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>232557</t>
+          <t>235035</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>279707</t>
+          <t>278745</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -6817,12 +6817,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>44,56%</t>
+          <t>45,03%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>53,59%</t>
+          <t>53,41%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -6837,12 +6837,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>52165</t>
+          <t>52833</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>79590</t>
+          <t>80656</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -6852,12 +6852,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>31,4%</t>
+          <t>31,8%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>47,91%</t>
+          <t>48,55%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -6872,12 +6872,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>297568</t>
+          <t>295903</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>351056</t>
+          <t>350458</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -6887,12 +6887,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>43,25%</t>
+          <t>43,01%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>51,02%</t>
+          <t>50,94%</t>
         </is>
       </c>
     </row>
@@ -7032,12 +7032,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>547447</t>
+          <t>543590</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>615804</t>
+          <t>611526</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -7047,12 +7047,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>47,62%</t>
+          <t>47,28%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>53,56%</t>
+          <t>53,19%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -7067,12 +7067,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>427983</t>
+          <t>429104</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>484688</t>
+          <t>485015</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -7082,12 +7082,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>51,82%</t>
+          <t>51,96%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>58,69%</t>
+          <t>58,73%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -7102,12 +7102,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>988295</t>
+          <t>997886</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>1083743</t>
+          <t>1082847</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -7117,12 +7117,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>50,03%</t>
+          <t>50,51%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>54,86%</t>
+          <t>54,81%</t>
         </is>
       </c>
     </row>
@@ -7145,12 +7145,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>533834</t>
+          <t>538112</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>602191</t>
+          <t>606048</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -7160,12 +7160,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>46,44%</t>
+          <t>46,81%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>52,38%</t>
+          <t>52,72%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -7180,12 +7180,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>341188</t>
+          <t>340861</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>397893</t>
+          <t>396772</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -7195,12 +7195,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>41,31%</t>
+          <t>41,27%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>48,18%</t>
+          <t>48,04%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -7215,12 +7215,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>891771</t>
+          <t>892667</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>987219</t>
+          <t>977628</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -7230,12 +7230,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>45,14%</t>
+          <t>45,19%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>49,97%</t>
+          <t>49,49%</t>
         </is>
       </c>
     </row>
@@ -7375,12 +7375,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>286452</t>
+          <t>289039</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>339711</t>
+          <t>337445</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -7390,12 +7390,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>46,15%</t>
+          <t>46,57%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>54,73%</t>
+          <t>54,36%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -7410,12 +7410,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>438434</t>
+          <t>436271</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>492621</t>
+          <t>493282</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -7425,12 +7425,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>59,39%</t>
+          <t>59,1%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>66,73%</t>
+          <t>66,82%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -7445,12 +7445,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>739884</t>
+          <t>739682</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>817551</t>
+          <t>816384</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -7460,12 +7460,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>54,45%</t>
+          <t>54,43%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>60,16%</t>
+          <t>60,07%</t>
         </is>
       </c>
     </row>
@@ -7488,12 +7488,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>280995</t>
+          <t>283261</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>334254</t>
+          <t>331667</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -7503,12 +7503,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>45,27%</t>
+          <t>45,64%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>53,85%</t>
+          <t>53,43%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -7523,12 +7523,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>245623</t>
+          <t>244962</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>299810</t>
+          <t>301973</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -7538,12 +7538,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>33,27%</t>
+          <t>33,18%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>40,61%</t>
+          <t>40,9%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -7558,12 +7558,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>541399</t>
+          <t>542566</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>619066</t>
+          <t>619268</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -7573,12 +7573,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>39,84%</t>
+          <t>39,93%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>45,55%</t>
+          <t>45,57%</t>
         </is>
       </c>
     </row>
@@ -7718,12 +7718,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>77301</t>
+          <t>78328</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>109325</t>
+          <t>108623</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -7733,12 +7733,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>26,92%</t>
+          <t>27,28%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>38,07%</t>
+          <t>37,83%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -7753,12 +7753,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>518861</t>
+          <t>517638</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>584664</t>
+          <t>583792</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -7768,12 +7768,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>47,95%</t>
+          <t>47,84%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>54,03%</t>
+          <t>53,95%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -7788,12 +7788,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>605902</t>
+          <t>601245</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>682960</t>
+          <t>681603</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -7803,12 +7803,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>44,25%</t>
+          <t>43,91%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>49,88%</t>
+          <t>49,78%</t>
         </is>
       </c>
     </row>
@@ -7831,12 +7831,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>177820</t>
+          <t>178522</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>209844</t>
+          <t>208817</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -7846,12 +7846,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>61,93%</t>
+          <t>62,17%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>73,08%</t>
+          <t>72,72%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -7866,12 +7866,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>497361</t>
+          <t>498233</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>563164</t>
+          <t>564387</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -7881,12 +7881,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>45,97%</t>
+          <t>46,05%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>52,05%</t>
+          <t>52,16%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -7901,12 +7901,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>686210</t>
+          <t>687567</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>763268</t>
+          <t>767925</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -7916,12 +7916,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>50,12%</t>
+          <t>50,22%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>55,75%</t>
+          <t>56,09%</t>
         </is>
       </c>
     </row>
@@ -8061,12 +8061,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>1571990</t>
+          <t>1570094</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>1688811</t>
+          <t>1691389</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -8076,12 +8076,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>46,43%</t>
+          <t>46,37%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>49,88%</t>
+          <t>49,96%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -8096,12 +8096,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>1880280</t>
+          <t>1879204</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>2000762</t>
+          <t>2002031</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -8111,12 +8111,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>53,24%</t>
+          <t>53,21%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>56,65%</t>
+          <t>56,69%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -8131,12 +8131,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>3484703</t>
+          <t>3488935</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>3657159</t>
+          <t>3657624</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -8146,12 +8146,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>50,38%</t>
+          <t>50,44%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>52,87%</t>
+          <t>52,88%</t>
         </is>
       </c>
     </row>
@@ -8174,12 +8174,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>1696911</t>
+          <t>1694333</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>1813732</t>
+          <t>1815628</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -8189,12 +8189,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>50,12%</t>
+          <t>50,04%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>53,57%</t>
+          <t>53,63%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -8209,12 +8209,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>1530834</t>
+          <t>1529565</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>1651316</t>
+          <t>1652392</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -8224,12 +8224,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>43,35%</t>
+          <t>43,31%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>46,76%</t>
+          <t>46,79%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -8244,12 +8244,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>3260159</t>
+          <t>3259694</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>3432615</t>
+          <t>3428383</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -8259,12 +8259,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>47,13%</t>
+          <t>47,12%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>49,62%</t>
+          <t>49,56%</t>
         </is>
       </c>
     </row>
@@ -8443,7 +8443,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población por debajo de la mediana (53.5790) de la puntuación del componente de salud mental (SF12) en 2023</t>
+          <t>Población por debajo de la mediana (53.579) de la puntuación del componente de salud mental (SF12) en 2023 (tasa de respuesta: 99,38%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -8638,12 +8638,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>186601</t>
+          <t>185402</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>232201</t>
+          <t>231597</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -8653,12 +8653,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>37,09%</t>
+          <t>36,86%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>46,16%</t>
+          <t>46,04%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -8673,12 +8673,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>181661</t>
+          <t>179289</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>216774</t>
+          <t>215093</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -8688,12 +8688,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>40,72%</t>
+          <t>40,18%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>48,58%</t>
+          <t>48,21%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -8708,12 +8708,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>380470</t>
+          <t>381295</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>437140</t>
+          <t>439304</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -8723,12 +8723,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>40,08%</t>
+          <t>40,17%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>46,05%</t>
+          <t>46,28%</t>
         </is>
       </c>
     </row>
@@ -8751,12 +8751,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>270849</t>
+          <t>271453</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>316449</t>
+          <t>317648</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -8766,12 +8766,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>53,84%</t>
+          <t>53,96%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>62,91%</t>
+          <t>63,14%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -8786,12 +8786,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>229402</t>
+          <t>231083</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>264515</t>
+          <t>266887</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -8801,12 +8801,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>51,42%</t>
+          <t>51,79%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>59,28%</t>
+          <t>59,82%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -8821,12 +8821,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>512086</t>
+          <t>509922</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>568756</t>
+          <t>567931</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -8836,12 +8836,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>53,95%</t>
+          <t>53,72%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>59,92%</t>
+          <t>59,83%</t>
         </is>
       </c>
     </row>
@@ -8981,12 +8981,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>144402</t>
+          <t>144150</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>186321</t>
+          <t>185933</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -8996,12 +8996,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>31,98%</t>
+          <t>31,93%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>41,27%</t>
+          <t>41,18%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -9016,12 +9016,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>171783</t>
+          <t>172879</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>204691</t>
+          <t>205054</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -9031,12 +9031,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>44,97%</t>
+          <t>45,26%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>53,58%</t>
+          <t>53,68%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -9051,12 +9051,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>325532</t>
+          <t>327589</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>380677</t>
+          <t>381267</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -9066,12 +9066,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>39,06%</t>
+          <t>39,3%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>45,67%</t>
+          <t>45,74%</t>
         </is>
       </c>
     </row>
@@ -9094,12 +9094,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>265161</t>
+          <t>265549</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>307080</t>
+          <t>307332</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -9109,12 +9109,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>58,73%</t>
+          <t>58,82%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>68,02%</t>
+          <t>68,07%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -9129,12 +9129,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>177315</t>
+          <t>176952</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>210223</t>
+          <t>209127</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -9144,12 +9144,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>46,42%</t>
+          <t>46,32%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>55,03%</t>
+          <t>54,74%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -9164,12 +9164,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>452810</t>
+          <t>452220</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>507955</t>
+          <t>505898</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -9179,12 +9179,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>54,33%</t>
+          <t>54,26%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>60,94%</t>
+          <t>60,7%</t>
         </is>
       </c>
     </row>
@@ -9324,12 +9324,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>65185</t>
+          <t>68038</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>305882</t>
+          <t>308981</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -9339,12 +9339,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>9,8%</t>
+          <t>10,23%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>45,97%</t>
+          <t>46,44%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -9359,12 +9359,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>79660</t>
+          <t>80101</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>99601</t>
+          <t>99694</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -9374,12 +9374,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>48,01%</t>
+          <t>48,28%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>60,03%</t>
+          <t>60,09%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -9394,12 +9394,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>117024</t>
+          <t>134658</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>406123</t>
+          <t>403570</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -9409,12 +9409,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>14,08%</t>
+          <t>16,2%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>48,85%</t>
+          <t>48,55%</t>
         </is>
       </c>
     </row>
@@ -9437,12 +9437,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>359486</t>
+          <t>356387</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>600183</t>
+          <t>597330</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -9452,12 +9452,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>54,03%</t>
+          <t>53,56%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>90,2%</t>
+          <t>89,77%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -9472,12 +9472,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>66320</t>
+          <t>66227</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>86261</t>
+          <t>85820</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -9487,12 +9487,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>39,97%</t>
+          <t>39,91%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>51,99%</t>
+          <t>51,72%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -9507,12 +9507,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>425166</t>
+          <t>427719</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>714265</t>
+          <t>696631</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -9522,12 +9522,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>51,15%</t>
+          <t>51,45%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>85,92%</t>
+          <t>83,8%</t>
         </is>
       </c>
     </row>
@@ -9667,12 +9667,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>405900</t>
+          <t>407484</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>474272</t>
+          <t>478087</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -9682,12 +9682,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>39,42%</t>
+          <t>39,57%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>46,06%</t>
+          <t>46,43%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -9702,12 +9702,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>464353</t>
+          <t>466903</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>770952</t>
+          <t>771325</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -9717,12 +9717,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>47,59%</t>
+          <t>47,85%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>79,01%</t>
+          <t>79,04%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -9737,12 +9737,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>893995</t>
+          <t>892954</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>1331290</t>
+          <t>1339211</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -9752,12 +9752,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>44,58%</t>
+          <t>44,52%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>66,38%</t>
+          <t>66,78%</t>
         </is>
       </c>
     </row>
@@ -9780,12 +9780,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>555448</t>
+          <t>551633</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>623820</t>
+          <t>622236</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -9795,12 +9795,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>53,94%</t>
+          <t>53,57%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>60,58%</t>
+          <t>60,43%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -9815,12 +9815,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>204874</t>
+          <t>204501</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>511473</t>
+          <t>508923</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -9830,12 +9830,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>20,99%</t>
+          <t>20,96%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>52,41%</t>
+          <t>52,15%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -9850,12 +9850,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>674257</t>
+          <t>666336</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1111552</t>
+          <t>1112593</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -9865,12 +9865,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>33,62%</t>
+          <t>33,22%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>55,42%</t>
+          <t>55,48%</t>
         </is>
       </c>
     </row>
@@ -10010,12 +10010,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>192565</t>
+          <t>194466</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>237965</t>
+          <t>240959</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -10025,12 +10025,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>40,93%</t>
+          <t>41,34%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>50,58%</t>
+          <t>51,22%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -10045,12 +10045,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>417650</t>
+          <t>419337</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>557175</t>
+          <t>562873</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -10060,12 +10060,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>49,92%</t>
+          <t>50,12%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>66,6%</t>
+          <t>67,28%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -10080,12 +10080,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>632197</t>
+          <t>634166</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>788387</t>
+          <t>795200</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -10095,12 +10095,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>48,37%</t>
+          <t>48,52%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>60,32%</t>
+          <t>60,84%</t>
         </is>
       </c>
     </row>
@@ -10123,12 +10123,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>232482</t>
+          <t>229488</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>277882</t>
+          <t>275981</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -10138,12 +10138,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>49,42%</t>
+          <t>48,78%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>59,07%</t>
+          <t>58,66%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -10158,12 +10158,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>279480</t>
+          <t>273782</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>419005</t>
+          <t>417318</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -10173,12 +10173,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>33,4%</t>
+          <t>32,72%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>50,08%</t>
+          <t>49,88%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -10193,12 +10193,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>518714</t>
+          <t>511901</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>674904</t>
+          <t>672935</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -10208,12 +10208,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>39,68%</t>
+          <t>39,16%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>51,63%</t>
+          <t>51,48%</t>
         </is>
       </c>
     </row>
@@ -10353,12 +10353,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>42707</t>
+          <t>45343</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>90311</t>
+          <t>94102</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -10368,12 +10368,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>17,76%</t>
+          <t>18,85%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>37,55%</t>
+          <t>39,13%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -10388,12 +10388,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>358162</t>
+          <t>358848</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>411380</t>
+          <t>409917</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -10403,12 +10403,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>47,59%</t>
+          <t>47,68%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>54,66%</t>
+          <t>54,47%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -10423,12 +10423,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>414384</t>
+          <t>406841</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>483058</t>
+          <t>480013</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -10438,12 +10438,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>41,73%</t>
+          <t>40,97%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>48,64%</t>
+          <t>48,33%</t>
         </is>
       </c>
     </row>
@@ -10466,12 +10466,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>150196</t>
+          <t>146405</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>197800</t>
+          <t>195164</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -10481,12 +10481,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>62,45%</t>
+          <t>60,87%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>82,24%</t>
+          <t>81,15%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -10501,12 +10501,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>341240</t>
+          <t>342703</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>394458</t>
+          <t>393772</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -10516,12 +10516,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>45,34%</t>
+          <t>45,53%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>52,41%</t>
+          <t>52,32%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -10536,12 +10536,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>510069</t>
+          <t>513114</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>578743</t>
+          <t>586286</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -10551,12 +10551,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>51,36%</t>
+          <t>51,67%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>58,27%</t>
+          <t>59,03%</t>
         </is>
       </c>
     </row>
@@ -10696,12 +10696,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>986894</t>
+          <t>980323</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>1409180</t>
+          <t>1405243</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -10711,12 +10711,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>29,37%</t>
+          <t>29,17%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>41,93%</t>
+          <t>41,82%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -10731,12 +10731,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>1779209</t>
+          <t>1774767</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>2239311</t>
+          <t>2234950</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -10746,12 +10746,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>49,99%</t>
+          <t>49,86%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>62,92%</t>
+          <t>62,79%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -10766,12 +10766,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>2862363</t>
+          <t>2868149</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>3516830</t>
+          <t>3513583</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -10781,12 +10781,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>41,36%</t>
+          <t>41,45%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>50,82%</t>
+          <t>50,78%</t>
         </is>
       </c>
     </row>
@@ -10809,12 +10809,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>1951394</t>
+          <t>1955331</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>2373680</t>
+          <t>2380251</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -10824,12 +10824,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>58,07%</t>
+          <t>58,18%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>70,63%</t>
+          <t>70,83%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -10844,12 +10844,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>1319893</t>
+          <t>1324254</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>1779995</t>
+          <t>1784437</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -10859,12 +10859,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>37,08%</t>
+          <t>37,21%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>50,01%</t>
+          <t>50,14%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -10879,12 +10879,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>3402948</t>
+          <t>3406195</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>4057415</t>
+          <t>4051629</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -10894,12 +10894,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>49,18%</t>
+          <t>49,22%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>58,64%</t>
+          <t>58,55%</t>
         </is>
       </c>
     </row>

--- a/data/trans_orig/MCS12_SP_R2-Clase-trans_orig.xlsx
+++ b/data/trans_orig/MCS12_SP_R2-Clase-trans_orig.xlsx
@@ -733,12 +733,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>172020</t>
+          <t>171343</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>215718</t>
+          <t>215957</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -748,12 +748,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>36,31%</t>
+          <t>36,17%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>45,53%</t>
+          <t>45,58%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -768,12 +768,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>139992</t>
+          <t>137140</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>172871</t>
+          <t>174010</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -783,12 +783,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>45,65%</t>
+          <t>44,72%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>56,37%</t>
+          <t>56,74%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -803,12 +803,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>319666</t>
+          <t>322229</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>376275</t>
+          <t>378112</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -818,12 +818,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>40,96%</t>
+          <t>41,29%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>48,21%</t>
+          <t>48,45%</t>
         </is>
       </c>
     </row>
@@ -846,12 +846,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>258058</t>
+          <t>257819</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>301756</t>
+          <t>302433</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -861,12 +861,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>54,47%</t>
+          <t>54,42%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>63,69%</t>
+          <t>63,83%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -881,12 +881,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>133809</t>
+          <t>132670</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>166688</t>
+          <t>169540</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -896,12 +896,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>43,63%</t>
+          <t>43,26%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>54,35%</t>
+          <t>55,28%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -916,12 +916,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>404182</t>
+          <t>402345</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>460791</t>
+          <t>458228</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -931,12 +931,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>51,79%</t>
+          <t>51,55%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>59,04%</t>
+          <t>58,71%</t>
         </is>
       </c>
     </row>
@@ -1076,12 +1076,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>124975</t>
+          <t>124567</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>162708</t>
+          <t>163719</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1091,12 +1091,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>34,06%</t>
+          <t>33,95%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>44,34%</t>
+          <t>44,62%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1111,12 +1111,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>186274</t>
+          <t>185790</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>225216</t>
+          <t>220601</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1126,12 +1126,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>50,09%</t>
+          <t>49,96%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>60,56%</t>
+          <t>59,32%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1146,12 +1146,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>319936</t>
+          <t>318786</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>375873</t>
+          <t>374392</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1161,12 +1161,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>43,3%</t>
+          <t>43,15%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>50,88%</t>
+          <t>50,68%</t>
         </is>
       </c>
     </row>
@@ -1189,12 +1189,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>204226</t>
+          <t>203215</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>241959</t>
+          <t>242367</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1204,12 +1204,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>55,66%</t>
+          <t>55,38%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>65,94%</t>
+          <t>66,05%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1224,12 +1224,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>146649</t>
+          <t>151264</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>185591</t>
+          <t>186075</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1239,12 +1239,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>39,44%</t>
+          <t>40,68%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>49,91%</t>
+          <t>50,04%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1259,12 +1259,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>362926</t>
+          <t>364407</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>418863</t>
+          <t>420013</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1274,12 +1274,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>49,12%</t>
+          <t>49,32%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>56,7%</t>
+          <t>56,85%</t>
         </is>
       </c>
     </row>
@@ -1419,12 +1419,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>221154</t>
+          <t>221874</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>264703</t>
+          <t>265470</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1434,12 +1434,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>40,77%</t>
+          <t>40,91%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>48,8%</t>
+          <t>48,94%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1454,12 +1454,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>83374</t>
+          <t>81756</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>108198</t>
+          <t>108445</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1469,12 +1469,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>49,69%</t>
+          <t>48,73%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>64,49%</t>
+          <t>64,63%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1489,12 +1489,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>314274</t>
+          <t>313253</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>363911</t>
+          <t>364470</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1504,12 +1504,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>44,25%</t>
+          <t>44,11%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>51,24%</t>
+          <t>51,32%</t>
         </is>
       </c>
     </row>
@@ -1532,12 +1532,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>277686</t>
+          <t>276919</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>321235</t>
+          <t>320515</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1547,12 +1547,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>51,2%</t>
+          <t>51,06%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>59,23%</t>
+          <t>59,09%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1567,12 +1567,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>59584</t>
+          <t>59337</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>84408</t>
+          <t>86026</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1582,12 +1582,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>35,51%</t>
+          <t>35,37%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>50,31%</t>
+          <t>51,27%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1602,12 +1602,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>346260</t>
+          <t>345701</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>395897</t>
+          <t>396918</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1617,12 +1617,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>48,76%</t>
+          <t>48,68%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>55,75%</t>
+          <t>55,89%</t>
         </is>
       </c>
     </row>
@@ -1762,12 +1762,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>560805</t>
+          <t>559505</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>629229</t>
+          <t>630044</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1777,12 +1777,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>45,29%</t>
+          <t>45,18%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>50,81%</t>
+          <t>50,88%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1797,12 +1797,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>354041</t>
+          <t>354916</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>411050</t>
+          <t>407568</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1812,12 +1812,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>49,57%</t>
+          <t>49,69%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>57,55%</t>
+          <t>57,06%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1832,12 +1832,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>937270</t>
+          <t>935588</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>1026198</t>
+          <t>1023209</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1847,12 +1847,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>48,0%</t>
+          <t>47,91%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>52,55%</t>
+          <t>52,4%</t>
         </is>
       </c>
     </row>
@@ -1875,12 +1875,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>609105</t>
+          <t>608290</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>677529</t>
+          <t>678829</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1890,12 +1890,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>49,19%</t>
+          <t>49,12%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>54,71%</t>
+          <t>54,82%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1910,12 +1910,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>303235</t>
+          <t>306717</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>360244</t>
+          <t>359369</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1925,12 +1925,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>42,45%</t>
+          <t>42,94%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>50,43%</t>
+          <t>50,31%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1945,12 +1945,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>926422</t>
+          <t>929411</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1015350</t>
+          <t>1017032</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1960,12 +1960,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>47,45%</t>
+          <t>47,6%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>52,0%</t>
+          <t>52,09%</t>
         </is>
       </c>
     </row>
@@ -2105,12 +2105,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>130915</t>
+          <t>130699</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>170269</t>
+          <t>169124</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2120,12 +2120,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>37,35%</t>
+          <t>37,28%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>48,57%</t>
+          <t>48,24%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2140,12 +2140,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>308518</t>
+          <t>305185</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>357102</t>
+          <t>356587</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2155,12 +2155,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>54,24%</t>
+          <t>53,66%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>62,79%</t>
+          <t>62,7%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2175,12 +2175,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>452046</t>
+          <t>455151</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>512003</t>
+          <t>513794</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2190,12 +2190,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>49,17%</t>
+          <t>49,51%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>55,69%</t>
+          <t>55,89%</t>
         </is>
       </c>
     </row>
@@ -2218,12 +2218,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>180286</t>
+          <t>181431</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>219640</t>
+          <t>219856</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2233,12 +2233,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>51,43%</t>
+          <t>51,76%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>62,65%</t>
+          <t>62,72%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2253,12 +2253,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>211650</t>
+          <t>212165</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>260234</t>
+          <t>263567</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2268,12 +2268,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>37,21%</t>
+          <t>37,3%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>45,76%</t>
+          <t>46,34%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2288,12 +2288,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>407304</t>
+          <t>405513</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>467261</t>
+          <t>464156</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2303,12 +2303,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>44,31%</t>
+          <t>44,11%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>50,83%</t>
+          <t>50,49%</t>
         </is>
       </c>
     </row>
@@ -2428,7 +2428,7 @@
     <row r="19">
       <c r="A19" s="1" t="inlineStr">
         <is>
-          <t>6.0</t>
+          <t>No ha trabajado</t>
         </is>
       </c>
       <c r="B19" s="3" t="inlineStr">
@@ -2448,12 +2448,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>70506</t>
+          <t>71348</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>101439</t>
+          <t>102678</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -2463,12 +2463,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>23,64%</t>
+          <t>23,93%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>34,02%</t>
+          <t>34,43%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2483,12 +2483,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>625518</t>
+          <t>622288</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>694322</t>
+          <t>692792</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -2498,12 +2498,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>50,09%</t>
+          <t>49,83%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>55,6%</t>
+          <t>55,48%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2518,12 +2518,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>707950</t>
+          <t>708939</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>783959</t>
+          <t>787161</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -2533,12 +2533,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>45,76%</t>
+          <t>45,83%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>50,68%</t>
+          <t>50,88%</t>
         </is>
       </c>
     </row>
@@ -2561,12 +2561,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>196762</t>
+          <t>195523</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>227695</t>
+          <t>226853</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2576,12 +2576,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>65,98%</t>
+          <t>65,57%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>76,36%</t>
+          <t>76,07%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2596,12 +2596,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>554438</t>
+          <t>555968</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>623242</t>
+          <t>626472</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2611,12 +2611,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>44,4%</t>
+          <t>44,52%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>49,91%</t>
+          <t>50,17%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2631,12 +2631,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>763001</t>
+          <t>759799</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>839010</t>
+          <t>838021</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2646,12 +2646,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>49,32%</t>
+          <t>49,12%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>54,24%</t>
+          <t>54,17%</t>
         </is>
       </c>
     </row>
@@ -2791,12 +2791,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>1358481</t>
+          <t>1360195</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>1471031</t>
+          <t>1471211</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2806,12 +2806,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>41,54%</t>
+          <t>41,59%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>44,98%</t>
+          <t>44,99%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2826,12 +2826,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>1772265</t>
+          <t>1769705</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>1889033</t>
+          <t>1887370</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2841,12 +2841,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>52,46%</t>
+          <t>52,39%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>55,92%</t>
+          <t>55,87%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2861,12 +2861,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>3170890</t>
+          <t>3162210</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>3326348</t>
+          <t>3333735</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2876,12 +2876,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>47,69%</t>
+          <t>47,56%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>50,03%</t>
+          <t>50,14%</t>
         </is>
       </c>
     </row>
@@ -2904,12 +2904,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>1799159</t>
+          <t>1798979</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>1911709</t>
+          <t>1909995</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -2919,12 +2919,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>55,02%</t>
+          <t>55,01%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>58,46%</t>
+          <t>58,41%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -2939,12 +2939,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>1489091</t>
+          <t>1490754</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>1605859</t>
+          <t>1608419</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -2954,12 +2954,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>44,08%</t>
+          <t>44,13%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>47,54%</t>
+          <t>47,61%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -2974,12 +2974,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>3321966</t>
+          <t>3314579</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>3477424</t>
+          <t>3486104</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -2989,12 +2989,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>49,97%</t>
+          <t>49,86%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>52,31%</t>
+          <t>52,44%</t>
         </is>
       </c>
     </row>
@@ -3368,12 +3368,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>198660</t>
+          <t>202428</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>243520</t>
+          <t>243324</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -3383,12 +3383,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>45,44%</t>
+          <t>46,3%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>55,7%</t>
+          <t>55,65%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -3403,12 +3403,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>157319</t>
+          <t>157737</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>195472</t>
+          <t>196063</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -3418,12 +3418,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>50,03%</t>
+          <t>50,16%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>62,16%</t>
+          <t>62,35%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -3438,12 +3438,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>372897</t>
+          <t>368240</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>430433</t>
+          <t>428078</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -3453,12 +3453,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>49,61%</t>
+          <t>48,99%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>57,26%</t>
+          <t>56,95%</t>
         </is>
       </c>
     </row>
@@ -3481,12 +3481,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>193691</t>
+          <t>193887</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>238551</t>
+          <t>234783</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -3496,12 +3496,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>44,3%</t>
+          <t>44,35%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>54,56%</t>
+          <t>53,7%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -3516,12 +3516,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>118982</t>
+          <t>118391</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>157135</t>
+          <t>156717</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -3531,12 +3531,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>37,84%</t>
+          <t>37,65%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>49,97%</t>
+          <t>49,84%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -3551,12 +3551,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>321232</t>
+          <t>323587</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>378768</t>
+          <t>383425</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -3566,12 +3566,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>42,74%</t>
+          <t>43,05%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>50,39%</t>
+          <t>51,01%</t>
         </is>
       </c>
     </row>
@@ -3711,12 +3711,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>180398</t>
+          <t>180918</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>223522</t>
+          <t>224081</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -3726,12 +3726,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>43,08%</t>
+          <t>43,2%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>53,37%</t>
+          <t>53,51%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -3746,12 +3746,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>197902</t>
+          <t>197674</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>235750</t>
+          <t>236004</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -3761,12 +3761,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>58,55%</t>
+          <t>58,48%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>69,75%</t>
+          <t>69,82%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -3781,12 +3781,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>390032</t>
+          <t>391003</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>447447</t>
+          <t>449292</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -3796,12 +3796,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>51,54%</t>
+          <t>51,66%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>59,12%</t>
+          <t>59,37%</t>
         </is>
       </c>
     </row>
@@ -3824,12 +3824,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>195275</t>
+          <t>194716</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>238399</t>
+          <t>237879</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -3839,12 +3839,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>46,63%</t>
+          <t>46,49%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>56,92%</t>
+          <t>56,8%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -3859,12 +3859,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>102261</t>
+          <t>102007</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>140109</t>
+          <t>140337</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -3874,12 +3874,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>30,25%</t>
+          <t>30,18%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>41,45%</t>
+          <t>41,52%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -3894,12 +3894,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>309361</t>
+          <t>307516</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>366776</t>
+          <t>365805</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -3909,12 +3909,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>40,88%</t>
+          <t>40,63%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>48,46%</t>
+          <t>48,34%</t>
         </is>
       </c>
     </row>
@@ -4054,12 +4054,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>306322</t>
+          <t>306964</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>359513</t>
+          <t>360663</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -4069,12 +4069,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>48,67%</t>
+          <t>48,77%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>57,12%</t>
+          <t>57,3%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -4089,12 +4089,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>155336</t>
+          <t>154865</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>186897</t>
+          <t>185773</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -4104,12 +4104,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>59,71%</t>
+          <t>59,53%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>71,85%</t>
+          <t>71,42%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -4124,12 +4124,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>473510</t>
+          <t>473007</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>536656</t>
+          <t>535580</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -4139,12 +4139,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>53,23%</t>
+          <t>53,17%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>60,33%</t>
+          <t>60,21%</t>
         </is>
       </c>
     </row>
@@ -4167,12 +4167,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>269902</t>
+          <t>268752</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>323093</t>
+          <t>322451</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -4182,12 +4182,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>42,88%</t>
+          <t>42,7%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>51,33%</t>
+          <t>51,23%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -4202,12 +4202,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>73232</t>
+          <t>74356</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>104793</t>
+          <t>105264</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -4217,12 +4217,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>28,15%</t>
+          <t>28,58%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>40,29%</t>
+          <t>40,47%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -4237,12 +4237,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>352888</t>
+          <t>353964</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>416034</t>
+          <t>416537</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -4252,12 +4252,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>39,67%</t>
+          <t>39,79%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>46,77%</t>
+          <t>46,83%</t>
         </is>
       </c>
     </row>
@@ -4397,12 +4397,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>559184</t>
+          <t>557624</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>631598</t>
+          <t>631880</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -4412,12 +4412,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>48,25%</t>
+          <t>48,11%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>54,49%</t>
+          <t>54,52%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -4432,12 +4432,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>435318</t>
+          <t>439357</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>493694</t>
+          <t>493612</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -4447,12 +4447,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>56,78%</t>
+          <t>57,31%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>64,4%</t>
+          <t>64,38%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -4467,12 +4467,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>1019743</t>
+          <t>1021425</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>1108702</t>
+          <t>1108549</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -4482,7 +4482,7 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>52,96%</t>
+          <t>53,04%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
@@ -4510,12 +4510,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>527411</t>
+          <t>527129</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>599825</t>
+          <t>601385</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -4525,12 +4525,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>45,51%</t>
+          <t>45,48%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>51,75%</t>
+          <t>51,89%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -4545,12 +4545,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>272963</t>
+          <t>273045</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>331339</t>
+          <t>327300</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -4560,12 +4560,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>35,6%</t>
+          <t>35,62%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>43,22%</t>
+          <t>42,69%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -4580,12 +4580,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>816965</t>
+          <t>817118</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>905924</t>
+          <t>904242</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -4600,7 +4600,7 @@
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>47,04%</t>
+          <t>46,96%</t>
         </is>
       </c>
     </row>
@@ -4740,12 +4740,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>214914</t>
+          <t>216216</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>261379</t>
+          <t>260911</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -4755,12 +4755,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>42,09%</t>
+          <t>42,35%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>51,19%</t>
+          <t>51,1%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -4775,12 +4775,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>465943</t>
+          <t>461652</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>517920</t>
+          <t>518130</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -4790,12 +4790,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>61,19%</t>
+          <t>60,62%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>68,01%</t>
+          <t>68,04%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -4810,12 +4810,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>697606</t>
+          <t>696370</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>768597</t>
+          <t>765360</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -4825,12 +4825,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>54,84%</t>
+          <t>54,74%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>60,42%</t>
+          <t>60,16%</t>
         </is>
       </c>
     </row>
@@ -4853,12 +4853,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>249217</t>
+          <t>249685</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>295682</t>
+          <t>294380</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -4868,12 +4868,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>48,81%</t>
+          <t>48,9%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>57,91%</t>
+          <t>57,65%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -4888,12 +4888,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>243602</t>
+          <t>243392</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>295579</t>
+          <t>299870</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -4903,12 +4903,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>31,99%</t>
+          <t>31,96%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>38,81%</t>
+          <t>39,38%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -4923,12 +4923,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>503521</t>
+          <t>506758</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>574512</t>
+          <t>575748</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -4938,12 +4938,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>39,58%</t>
+          <t>39,84%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>45,16%</t>
+          <t>45,26%</t>
         </is>
       </c>
     </row>
@@ -5063,7 +5063,7 @@
     <row r="19">
       <c r="A19" s="1" t="inlineStr">
         <is>
-          <t>6.0</t>
+          <t>No ha trabajado</t>
         </is>
       </c>
       <c r="B19" s="3" t="inlineStr">
@@ -5083,12 +5083,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>71178</t>
+          <t>71229</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>102671</t>
+          <t>102083</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -5098,12 +5098,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>26,67%</t>
+          <t>26,69%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>38,47%</t>
+          <t>38,25%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -5118,12 +5118,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>636342</t>
+          <t>636596</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>702602</t>
+          <t>700106</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -5133,12 +5133,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>57,36%</t>
+          <t>57,38%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>63,33%</t>
+          <t>63,11%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -5153,12 +5153,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>718721</t>
+          <t>720361</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>794843</t>
+          <t>793129</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -5168,12 +5168,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>52,22%</t>
+          <t>52,34%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>57,75%</t>
+          <t>57,63%</t>
         </is>
       </c>
     </row>
@@ -5196,12 +5196,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>164211</t>
+          <t>164799</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>195704</t>
+          <t>195653</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -5211,12 +5211,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>61,53%</t>
+          <t>61,75%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>73,33%</t>
+          <t>73,31%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -5231,12 +5231,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>406749</t>
+          <t>409245</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>473009</t>
+          <t>472755</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -5246,12 +5246,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>36,67%</t>
+          <t>36,89%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>42,64%</t>
+          <t>42,62%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -5266,12 +5266,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>581390</t>
+          <t>583104</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>657512</t>
+          <t>655872</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -5281,12 +5281,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>42,25%</t>
+          <t>42,37%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>47,78%</t>
+          <t>47,66%</t>
         </is>
       </c>
     </row>
@@ -5426,12 +5426,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>1624206</t>
+          <t>1616654</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>1738806</t>
+          <t>1737584</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -5441,12 +5441,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>47,46%</t>
+          <t>47,24%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>50,81%</t>
+          <t>50,78%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -5461,12 +5461,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>2135351</t>
+          <t>2136163</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>2257824</t>
+          <t>2258275</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -5476,12 +5476,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>60,15%</t>
+          <t>60,17%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>63,6%</t>
+          <t>63,61%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -5496,12 +5496,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>3782405</t>
+          <t>3781642</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>3961541</t>
+          <t>3955352</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -5511,12 +5511,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>54,25%</t>
+          <t>54,24%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>56,82%</t>
+          <t>56,73%</t>
         </is>
       </c>
     </row>
@@ -5539,12 +5539,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>1683104</t>
+          <t>1684326</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>1797704</t>
+          <t>1805256</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -5554,12 +5554,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>49,19%</t>
+          <t>49,22%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>52,54%</t>
+          <t>52,76%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -5574,12 +5574,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>1292301</t>
+          <t>1291850</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>1414774</t>
+          <t>1413962</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -5589,12 +5589,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>36,4%</t>
+          <t>36,39%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>39,85%</t>
+          <t>39,83%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -5609,12 +5609,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>3010494</t>
+          <t>3016683</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>3189630</t>
+          <t>3190393</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -5624,12 +5624,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>43,18%</t>
+          <t>43,27%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>45,75%</t>
+          <t>45,76%</t>
         </is>
       </c>
     </row>
@@ -6003,12 +6003,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>181553</t>
+          <t>183005</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>225817</t>
+          <t>226453</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -6018,12 +6018,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>42,31%</t>
+          <t>42,65%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>52,63%</t>
+          <t>52,77%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -6038,12 +6038,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>147978</t>
+          <t>149811</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>186190</t>
+          <t>187568</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -6053,12 +6053,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>42,64%</t>
+          <t>43,17%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>53,65%</t>
+          <t>54,05%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -6073,12 +6073,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>345409</t>
+          <t>345041</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>401286</t>
+          <t>401407</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -6088,12 +6088,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>44,5%</t>
+          <t>44,46%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>51,7%</t>
+          <t>51,72%</t>
         </is>
       </c>
     </row>
@@ -6116,12 +6116,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>203275</t>
+          <t>202639</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>247539</t>
+          <t>246087</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -6131,12 +6131,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>47,37%</t>
+          <t>47,23%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>57,69%</t>
+          <t>57,35%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -6151,12 +6151,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>160865</t>
+          <t>159487</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>199077</t>
+          <t>197244</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -6166,12 +6166,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>46,35%</t>
+          <t>45,95%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>57,36%</t>
+          <t>56,83%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -6186,12 +6186,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>374861</t>
+          <t>374740</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>430738</t>
+          <t>431106</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -6201,12 +6201,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>48,3%</t>
+          <t>48,28%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>55,5%</t>
+          <t>55,54%</t>
         </is>
       </c>
     </row>
@@ -6346,12 +6346,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>155381</t>
+          <t>153947</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>193907</t>
+          <t>193742</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -6361,12 +6361,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>41,19%</t>
+          <t>40,81%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>51,4%</t>
+          <t>51,36%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -6381,12 +6381,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>178043</t>
+          <t>177779</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>217626</t>
+          <t>218071</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -6396,12 +6396,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>47,83%</t>
+          <t>47,75%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>58,46%</t>
+          <t>58,58%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -6416,12 +6416,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>345815</t>
+          <t>344016</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>401136</t>
+          <t>400799</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -6431,12 +6431,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>46,14%</t>
+          <t>45,9%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>53,52%</t>
+          <t>53,48%</t>
         </is>
       </c>
     </row>
@@ -6459,12 +6459,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>183320</t>
+          <t>183485</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>221846</t>
+          <t>223280</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -6474,12 +6474,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>48,6%</t>
+          <t>48,64%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>58,81%</t>
+          <t>59,19%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -6494,12 +6494,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>154647</t>
+          <t>154202</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>194230</t>
+          <t>194494</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -6509,12 +6509,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>41,54%</t>
+          <t>41,42%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>52,17%</t>
+          <t>52,25%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -6529,12 +6529,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>348364</t>
+          <t>348701</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>403685</t>
+          <t>405484</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -6544,12 +6544,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>46,48%</t>
+          <t>46,52%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>53,86%</t>
+          <t>54,1%</t>
         </is>
       </c>
     </row>
@@ -6689,12 +6689,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>243169</t>
+          <t>243358</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>286879</t>
+          <t>289418</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -6704,12 +6704,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>46,59%</t>
+          <t>46,63%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>54,97%</t>
+          <t>55,45%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -6724,12 +6724,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>85467</t>
+          <t>87131</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>113290</t>
+          <t>113292</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -6739,7 +6739,7 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>51,45%</t>
+          <t>52,45%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
@@ -6759,12 +6759,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>337578</t>
+          <t>337579</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>392133</t>
+          <t>391934</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -6779,7 +6779,7 @@
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>56,99%</t>
+          <t>56,96%</t>
         </is>
       </c>
     </row>
@@ -6802,12 +6802,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>235035</t>
+          <t>232496</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>278745</t>
+          <t>278556</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -6817,12 +6817,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>45,03%</t>
+          <t>44,55%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>53,41%</t>
+          <t>53,37%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -6837,12 +6837,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>52833</t>
+          <t>52831</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>80656</t>
+          <t>78992</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -6857,7 +6857,7 @@
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>48,55%</t>
+          <t>47,55%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -6872,12 +6872,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>295903</t>
+          <t>296102</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>350458</t>
+          <t>350457</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -6887,7 +6887,7 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>43,01%</t>
+          <t>43,04%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
@@ -7032,12 +7032,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>543590</t>
+          <t>545361</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>611526</t>
+          <t>613775</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -7047,12 +7047,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>47,28%</t>
+          <t>47,44%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>53,19%</t>
+          <t>53,39%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -7067,12 +7067,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>429104</t>
+          <t>428230</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>485015</t>
+          <t>483766</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -7082,12 +7082,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>51,96%</t>
+          <t>51,85%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>58,73%</t>
+          <t>58,58%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -7102,12 +7102,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>997886</t>
+          <t>989548</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>1082847</t>
+          <t>1077294</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -7117,12 +7117,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>50,51%</t>
+          <t>50,09%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>54,81%</t>
+          <t>54,53%</t>
         </is>
       </c>
     </row>
@@ -7145,12 +7145,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>538112</t>
+          <t>535863</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>606048</t>
+          <t>604277</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -7160,12 +7160,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>46,81%</t>
+          <t>46,61%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>52,72%</t>
+          <t>52,56%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -7180,12 +7180,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>340861</t>
+          <t>342110</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>396772</t>
+          <t>397646</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -7195,12 +7195,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>41,27%</t>
+          <t>41,42%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>48,04%</t>
+          <t>48,15%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -7215,12 +7215,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>892667</t>
+          <t>898220</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>977628</t>
+          <t>985966</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -7230,12 +7230,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>45,19%</t>
+          <t>45,47%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>49,49%</t>
+          <t>49,91%</t>
         </is>
       </c>
     </row>
@@ -7375,12 +7375,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>289039</t>
+          <t>287366</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>337445</t>
+          <t>339338</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -7390,12 +7390,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>46,57%</t>
+          <t>46,3%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>54,36%</t>
+          <t>54,67%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -7410,12 +7410,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>436271</t>
+          <t>436844</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>493282</t>
+          <t>491338</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -7425,12 +7425,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>59,1%</t>
+          <t>59,17%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>66,82%</t>
+          <t>66,55%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -7445,12 +7445,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>739682</t>
+          <t>740968</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>816384</t>
+          <t>812741</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -7460,12 +7460,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>54,43%</t>
+          <t>54,53%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>60,07%</t>
+          <t>59,81%</t>
         </is>
       </c>
     </row>
@@ -7488,12 +7488,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>283261</t>
+          <t>281368</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>331667</t>
+          <t>333340</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -7503,12 +7503,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>45,64%</t>
+          <t>45,33%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>53,43%</t>
+          <t>53,7%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -7523,12 +7523,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>244962</t>
+          <t>246906</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>301973</t>
+          <t>301400</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -7538,12 +7538,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>33,18%</t>
+          <t>33,45%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>40,9%</t>
+          <t>40,83%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -7558,12 +7558,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>542566</t>
+          <t>546209</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>619268</t>
+          <t>617982</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -7573,12 +7573,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>39,93%</t>
+          <t>40,19%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>45,57%</t>
+          <t>45,47%</t>
         </is>
       </c>
     </row>
@@ -7698,7 +7698,7 @@
     <row r="19">
       <c r="A19" s="1" t="inlineStr">
         <is>
-          <t>6.0</t>
+          <t>No ha trabajado</t>
         </is>
       </c>
       <c r="B19" s="3" t="inlineStr">
@@ -7718,12 +7718,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>78328</t>
+          <t>77788</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>108623</t>
+          <t>109851</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -7733,12 +7733,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>27,28%</t>
+          <t>27,09%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>37,83%</t>
+          <t>38,26%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -7753,12 +7753,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>517638</t>
+          <t>519251</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>583792</t>
+          <t>582975</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -7768,12 +7768,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>47,84%</t>
+          <t>47,99%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>53,95%</t>
+          <t>53,88%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -7788,12 +7788,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>601245</t>
+          <t>605659</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>681603</t>
+          <t>679560</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -7803,12 +7803,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>43,91%</t>
+          <t>44,24%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>49,78%</t>
+          <t>49,63%</t>
         </is>
       </c>
     </row>
@@ -7831,12 +7831,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>178522</t>
+          <t>177294</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>208817</t>
+          <t>209357</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -7846,12 +7846,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>62,17%</t>
+          <t>61,74%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>72,72%</t>
+          <t>72,91%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -7866,12 +7866,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>498233</t>
+          <t>499050</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>564387</t>
+          <t>562774</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -7881,12 +7881,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>46,05%</t>
+          <t>46,12%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>52,16%</t>
+          <t>52,01%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -7901,12 +7901,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>687567</t>
+          <t>689610</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>767925</t>
+          <t>763511</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -7916,12 +7916,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>50,22%</t>
+          <t>50,37%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>56,09%</t>
+          <t>55,76%</t>
         </is>
       </c>
     </row>
@@ -8061,12 +8061,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>1570094</t>
+          <t>1574892</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>1691389</t>
+          <t>1688535</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -8076,12 +8076,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>46,37%</t>
+          <t>46,52%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>49,96%</t>
+          <t>49,87%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -8096,12 +8096,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>1879204</t>
+          <t>1876969</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>2002031</t>
+          <t>1998196</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -8111,12 +8111,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>53,21%</t>
+          <t>53,15%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>56,69%</t>
+          <t>56,58%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -8131,12 +8131,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>3488935</t>
+          <t>3485543</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>3657624</t>
+          <t>3662135</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -8146,12 +8146,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>50,44%</t>
+          <t>50,39%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>52,88%</t>
+          <t>52,94%</t>
         </is>
       </c>
     </row>
@@ -8174,12 +8174,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>1694333</t>
+          <t>1697187</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>1815628</t>
+          <t>1810830</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -8189,12 +8189,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>50,04%</t>
+          <t>50,13%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>53,63%</t>
+          <t>53,48%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -8209,12 +8209,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>1529565</t>
+          <t>1533400</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>1652392</t>
+          <t>1654627</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -8224,12 +8224,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>43,31%</t>
+          <t>43,42%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>46,79%</t>
+          <t>46,85%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -8244,12 +8244,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>3259694</t>
+          <t>3255183</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>3428383</t>
+          <t>3431775</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -8259,12 +8259,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>47,12%</t>
+          <t>47,06%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>49,56%</t>
+          <t>49,61%</t>
         </is>
       </c>
     </row>
@@ -8633,32 +8633,32 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>209885</t>
+          <t>228052</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>185402</t>
+          <t>205261</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>231597</t>
+          <t>253758</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>41,72%</t>
+          <t>41,6%</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>36,86%</t>
+          <t>37,45%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>46,04%</t>
+          <t>46,29%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -8668,32 +8668,32 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>198646</t>
+          <t>220696</t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>179289</t>
+          <t>200991</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>215093</t>
+          <t>240810</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>44,52%</t>
+          <t>45,33%</t>
         </is>
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>40,18%</t>
+          <t>41,29%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>48,21%</t>
+          <t>49,47%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -8703,32 +8703,32 @@
       </c>
       <c r="R4" s="2" t="inlineStr">
         <is>
-          <t>408532</t>
+          <t>448748</t>
         </is>
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>381295</t>
+          <t>419765</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>439304</t>
+          <t>481310</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
         <is>
-          <t>43,04%</t>
+          <t>43,36%</t>
         </is>
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>40,17%</t>
+          <t>40,56%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>46,28%</t>
+          <t>46,5%</t>
         </is>
       </c>
     </row>
@@ -8746,32 +8746,32 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>293165</t>
+          <t>320113</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>271453</t>
+          <t>294407</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>317648</t>
+          <t>342904</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>58,28%</t>
+          <t>58,4%</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>53,96%</t>
+          <t>53,71%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>63,14%</t>
+          <t>62,55%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -8781,32 +8781,32 @@
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>247530</t>
+          <t>266125</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>231083</t>
+          <t>246011</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>266887</t>
+          <t>285830</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>55,48%</t>
+          <t>54,67%</t>
         </is>
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>51,79%</t>
+          <t>50,53%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>59,82%</t>
+          <t>58,71%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -8816,32 +8816,32 @@
       </c>
       <c r="R5" s="2" t="inlineStr">
         <is>
-          <t>540694</t>
+          <t>586239</t>
         </is>
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>509922</t>
+          <t>553677</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>567931</t>
+          <t>615222</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
         <is>
-          <t>56,96%</t>
+          <t>56,64%</t>
         </is>
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>53,72%</t>
+          <t>53,5%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>59,83%</t>
+          <t>59,44%</t>
         </is>
       </c>
     </row>
@@ -8859,17 +8859,17 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>503050</t>
+          <t>548165</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>503050</t>
+          <t>548165</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>503050</t>
+          <t>548165</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -8894,17 +8894,17 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>446176</t>
+          <t>486821</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>446176</t>
+          <t>486821</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>446176</t>
+          <t>486821</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -8929,17 +8929,17 @@
       </c>
       <c r="R6" s="2" t="inlineStr">
         <is>
-          <t>949226</t>
+          <t>1034987</t>
         </is>
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>949226</t>
+          <t>1034987</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>949226</t>
+          <t>1034987</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -8976,32 +8976,32 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>165191</t>
+          <t>175940</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>144150</t>
+          <t>154507</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>185933</t>
+          <t>195801</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>36,59%</t>
+          <t>36,49%</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>31,93%</t>
+          <t>32,04%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>41,18%</t>
+          <t>40,61%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -9011,22 +9011,22 @@
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>188518</t>
+          <t>208863</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>172879</t>
+          <t>191226</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>205054</t>
+          <t>228134</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>49,35%</t>
+          <t>49,44%</t>
         </is>
       </c>
       <c r="O7" s="2" t="inlineStr">
@@ -9036,7 +9036,7 @@
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>53,68%</t>
+          <t>54,0%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -9046,32 +9046,32 @@
       </c>
       <c r="R7" s="2" t="inlineStr">
         <is>
-          <t>353708</t>
+          <t>384803</t>
         </is>
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>327589</t>
+          <t>356551</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>381267</t>
+          <t>411726</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
         <is>
-          <t>42,44%</t>
+          <t>42,53%</t>
         </is>
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>39,3%</t>
+          <t>39,41%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>45,74%</t>
+          <t>45,51%</t>
         </is>
       </c>
     </row>
@@ -9089,32 +9089,32 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>286291</t>
+          <t>306268</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>265549</t>
+          <t>286407</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>307332</t>
+          <t>327701</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>63,41%</t>
+          <t>63,51%</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>58,82%</t>
+          <t>59,39%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>68,07%</t>
+          <t>67,96%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -9124,27 +9124,27 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>193488</t>
+          <t>213623</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>176952</t>
+          <t>194352</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>209127</t>
+          <t>231260</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>50,65%</t>
+          <t>50,56%</t>
         </is>
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>46,32%</t>
+          <t>46,0%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
@@ -9159,32 +9159,32 @@
       </c>
       <c r="R8" s="2" t="inlineStr">
         <is>
-          <t>479779</t>
+          <t>519891</t>
         </is>
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>452220</t>
+          <t>492968</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>505898</t>
+          <t>548143</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
         <is>
-          <t>57,56%</t>
+          <t>57,47%</t>
         </is>
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>54,26%</t>
+          <t>54,49%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>60,7%</t>
+          <t>60,59%</t>
         </is>
       </c>
     </row>
@@ -9202,17 +9202,17 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>451482</t>
+          <t>482208</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>451482</t>
+          <t>482208</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>451482</t>
+          <t>482208</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -9237,17 +9237,17 @@
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>382006</t>
+          <t>422486</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>382006</t>
+          <t>422486</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>382006</t>
+          <t>422486</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -9272,17 +9272,17 @@
       </c>
       <c r="R9" s="2" t="inlineStr">
         <is>
-          <t>833487</t>
+          <t>904694</t>
         </is>
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>833487</t>
+          <t>904694</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>833487</t>
+          <t>904694</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -9319,32 +9319,32 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>189133</t>
+          <t>210048</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>68038</t>
+          <t>188727</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>308981</t>
+          <t>231904</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>28,43%</t>
+          <t>44,82%</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>10,23%</t>
+          <t>40,27%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>46,44%</t>
+          <t>49,48%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -9354,32 +9354,32 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>89742</t>
+          <t>101047</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>80101</t>
+          <t>90719</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>99694</t>
+          <t>113002</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>54,09%</t>
+          <t>54,2%</t>
         </is>
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>48,28%</t>
+          <t>48,66%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>60,09%</t>
+          <t>60,61%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -9389,32 +9389,32 @@
       </c>
       <c r="R10" s="2" t="inlineStr">
         <is>
-          <t>278874</t>
+          <t>311096</t>
         </is>
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>134658</t>
+          <t>286429</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>403570</t>
+          <t>335227</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
         <is>
-          <t>33,55%</t>
+          <t>47,49%</t>
         </is>
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>16,2%</t>
+          <t>43,72%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>48,55%</t>
+          <t>51,17%</t>
         </is>
       </c>
     </row>
@@ -9432,32 +9432,32 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>476235</t>
+          <t>258620</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>356387</t>
+          <t>236764</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>597330</t>
+          <t>279941</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>71,57%</t>
+          <t>55,18%</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>53,56%</t>
+          <t>50,52%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>89,77%</t>
+          <t>59,73%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -9467,32 +9467,32 @@
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>76179</t>
+          <t>85402</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>66227</t>
+          <t>73447</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>85820</t>
+          <t>95730</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>45,91%</t>
+          <t>45,8%</t>
         </is>
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>39,91%</t>
+          <t>39,39%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>51,72%</t>
+          <t>51,34%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -9502,32 +9502,32 @@
       </c>
       <c r="R11" s="2" t="inlineStr">
         <is>
-          <t>552415</t>
+          <t>344022</t>
         </is>
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>427719</t>
+          <t>319891</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>696631</t>
+          <t>368689</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
         <is>
-          <t>66,45%</t>
+          <t>52,51%</t>
         </is>
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>51,45%</t>
+          <t>48,83%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>83,8%</t>
+          <t>56,28%</t>
         </is>
       </c>
     </row>
@@ -9545,17 +9545,17 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>665368</t>
+          <t>468668</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>665368</t>
+          <t>468668</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>665368</t>
+          <t>468668</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -9580,17 +9580,17 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>165921</t>
+          <t>186449</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>165921</t>
+          <t>186449</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>165921</t>
+          <t>186449</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -9615,17 +9615,17 @@
       </c>
       <c r="R12" s="2" t="inlineStr">
         <is>
-          <t>831289</t>
+          <t>655118</t>
         </is>
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>831289</t>
+          <t>655118</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>831289</t>
+          <t>655118</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -9662,67 +9662,67 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>441917</t>
+          <t>487706</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>407484</t>
+          <t>453456</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>478087</t>
+          <t>526233</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>42,92%</t>
+          <t>43,3%</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>39,57%</t>
+          <t>40,26%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
+          <t>46,72%</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
+          <t>645</t>
+        </is>
+      </c>
+      <c r="K13" s="2" t="inlineStr">
+        <is>
+          <t>424846</t>
+        </is>
+      </c>
+      <c r="L13" s="2" t="inlineStr">
+        <is>
+          <t>398801</t>
+        </is>
+      </c>
+      <c r="M13" s="2" t="inlineStr">
+        <is>
+          <t>454188</t>
+        </is>
+      </c>
+      <c r="N13" s="2" t="inlineStr">
+        <is>
+          <t>49,47%</t>
+        </is>
+      </c>
+      <c r="O13" s="2" t="inlineStr">
+        <is>
           <t>46,43%</t>
         </is>
       </c>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t>645</t>
-        </is>
-      </c>
-      <c r="K13" s="2" t="inlineStr">
-        <is>
-          <t>579007</t>
-        </is>
-      </c>
-      <c r="L13" s="2" t="inlineStr">
-        <is>
-          <t>466903</t>
-        </is>
-      </c>
-      <c r="M13" s="2" t="inlineStr">
-        <is>
-          <t>771325</t>
-        </is>
-      </c>
-      <c r="N13" s="2" t="inlineStr">
-        <is>
-          <t>59,34%</t>
-        </is>
-      </c>
-      <c r="O13" s="2" t="inlineStr">
-        <is>
-          <t>47,85%</t>
-        </is>
-      </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>79,04%</t>
+          <t>52,88%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -9732,32 +9732,32 @@
       </c>
       <c r="R13" s="2" t="inlineStr">
         <is>
-          <t>1020925</t>
+          <t>912551</t>
         </is>
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>892954</t>
+          <t>869386</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>1339211</t>
+          <t>954798</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
         <is>
-          <t>50,91%</t>
+          <t>45,97%</t>
         </is>
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>44,52%</t>
+          <t>43,79%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>66,78%</t>
+          <t>48,1%</t>
         </is>
       </c>
     </row>
@@ -9775,69 +9775,69 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>587803</t>
+          <t>638574</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>551633</t>
+          <t>600047</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>622236</t>
+          <t>672824</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>57,08%</t>
+          <t>56,7%</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
+          <t>53,28%</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>59,74%</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
+          <t>580</t>
+        </is>
+      </c>
+      <c r="K14" s="2" t="inlineStr">
+        <is>
+          <t>434025</t>
+        </is>
+      </c>
+      <c r="L14" s="2" t="inlineStr">
+        <is>
+          <t>404683</t>
+        </is>
+      </c>
+      <c r="M14" s="2" t="inlineStr">
+        <is>
+          <t>460070</t>
+        </is>
+      </c>
+      <c r="N14" s="2" t="inlineStr">
+        <is>
+          <t>50,53%</t>
+        </is>
+      </c>
+      <c r="O14" s="2" t="inlineStr">
+        <is>
+          <t>47,12%</t>
+        </is>
+      </c>
+      <c r="P14" s="2" t="inlineStr">
+        <is>
           <t>53,57%</t>
         </is>
       </c>
-      <c r="I14" s="2" t="inlineStr">
-        <is>
-          <t>60,43%</t>
-        </is>
-      </c>
-      <c r="J14" s="2" t="inlineStr">
-        <is>
-          <t>580</t>
-        </is>
-      </c>
-      <c r="K14" s="2" t="inlineStr">
-        <is>
-          <t>396819</t>
-        </is>
-      </c>
-      <c r="L14" s="2" t="inlineStr">
-        <is>
-          <t>204501</t>
-        </is>
-      </c>
-      <c r="M14" s="2" t="inlineStr">
-        <is>
-          <t>508923</t>
-        </is>
-      </c>
-      <c r="N14" s="2" t="inlineStr">
-        <is>
-          <t>40,66%</t>
-        </is>
-      </c>
-      <c r="O14" s="2" t="inlineStr">
-        <is>
-          <t>20,96%</t>
-        </is>
-      </c>
-      <c r="P14" s="2" t="inlineStr">
-        <is>
-          <t>52,15%</t>
-        </is>
-      </c>
       <c r="Q14" s="2" t="inlineStr">
         <is>
           <t>1181</t>
@@ -9845,32 +9845,32 @@
       </c>
       <c r="R14" s="2" t="inlineStr">
         <is>
-          <t>984622</t>
+          <t>1072600</t>
         </is>
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>666336</t>
+          <t>1030353</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1112593</t>
+          <t>1115765</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
         <is>
-          <t>49,09%</t>
+          <t>54,03%</t>
         </is>
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>33,22%</t>
+          <t>51,9%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>55,48%</t>
+          <t>56,21%</t>
         </is>
       </c>
     </row>
@@ -9888,17 +9888,17 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>1029720</t>
+          <t>1126280</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>1029720</t>
+          <t>1126280</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>1029720</t>
+          <t>1126280</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -9923,17 +9923,17 @@
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>975826</t>
+          <t>858871</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>975826</t>
+          <t>858871</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>975826</t>
+          <t>858871</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -9958,17 +9958,17 @@
       </c>
       <c r="R15" s="2" t="inlineStr">
         <is>
-          <t>2005547</t>
+          <t>1985151</t>
         </is>
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>2005547</t>
+          <t>1985151</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>2005547</t>
+          <t>1985151</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -10005,32 +10005,32 @@
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>217614</t>
+          <t>255103</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>194466</t>
+          <t>228564</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>240959</t>
+          <t>281885</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t>46,26%</t>
+          <t>45,32%</t>
         </is>
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>41,34%</t>
+          <t>40,6%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>51,22%</t>
+          <t>50,07%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -10040,32 +10040,32 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>473535</t>
+          <t>453873</t>
         </is>
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>419337</t>
+          <t>431228</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>562873</t>
+          <t>479593</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>56,6%</t>
+          <t>54,95%</t>
         </is>
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>50,12%</t>
+          <t>52,21%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>67,28%</t>
+          <t>58,07%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -10075,32 +10075,32 @@
       </c>
       <c r="R16" s="2" t="inlineStr">
         <is>
-          <t>691148</t>
+          <t>708977</t>
         </is>
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>634166</t>
+          <t>670066</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>795200</t>
+          <t>744640</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
         <is>
-          <t>52,88%</t>
+          <t>51,05%</t>
         </is>
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>48,52%</t>
+          <t>48,24%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>60,84%</t>
+          <t>53,61%</t>
         </is>
       </c>
     </row>
@@ -10118,32 +10118,32 @@
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>252833</t>
+          <t>307832</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>229488</t>
+          <t>281050</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>275981</t>
+          <t>334371</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>53,74%</t>
+          <t>54,68%</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>48,78%</t>
+          <t>49,93%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>58,66%</t>
+          <t>59,4%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -10153,32 +10153,32 @@
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>363120</t>
+          <t>372084</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>273782</t>
+          <t>346364</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>417318</t>
+          <t>394729</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>43,4%</t>
+          <t>45,05%</t>
         </is>
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>32,72%</t>
+          <t>41,93%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>49,88%</t>
+          <t>47,79%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -10188,32 +10188,32 @@
       </c>
       <c r="R17" s="2" t="inlineStr">
         <is>
-          <t>615953</t>
+          <t>679915</t>
         </is>
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>511901</t>
+          <t>644252</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>672935</t>
+          <t>718826</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
         <is>
-          <t>47,12%</t>
+          <t>48,95%</t>
         </is>
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>39,16%</t>
+          <t>46,39%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>51,48%</t>
+          <t>51,76%</t>
         </is>
       </c>
     </row>
@@ -10231,17 +10231,17 @@
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>470447</t>
+          <t>562935</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>470447</t>
+          <t>562935</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>470447</t>
+          <t>562935</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -10266,17 +10266,17 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>836655</t>
+          <t>825957</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>836655</t>
+          <t>825957</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>836655</t>
+          <t>825957</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -10301,17 +10301,17 @@
       </c>
       <c r="R18" s="2" t="inlineStr">
         <is>
-          <t>1307101</t>
+          <t>1388892</t>
         </is>
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>1307101</t>
+          <t>1388892</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>1307101</t>
+          <t>1388892</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -10333,7 +10333,7 @@
     <row r="19">
       <c r="A19" s="1" t="inlineStr">
         <is>
-          <t>6.0</t>
+          <t>No ha trabajado</t>
         </is>
       </c>
       <c r="B19" s="3" t="inlineStr">
@@ -10348,32 +10348,32 @@
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>64403</t>
+          <t>68526</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>45343</t>
+          <t>50022</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>94102</t>
+          <t>92621</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>26,78%</t>
+          <t>28,89%</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>18,85%</t>
+          <t>21,09%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>39,13%</t>
+          <t>39,04%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -10383,32 +10383,32 @@
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>383677</t>
+          <t>421802</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>358848</t>
+          <t>390805</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>409917</t>
+          <t>448531</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>50,98%</t>
+          <t>50,5%</t>
         </is>
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>47,68%</t>
+          <t>46,79%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>54,47%</t>
+          <t>53,7%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -10418,32 +10418,32 @@
       </c>
       <c r="R19" s="2" t="inlineStr">
         <is>
-          <t>448080</t>
+          <t>490329</t>
         </is>
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>406841</t>
+          <t>452919</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>480013</t>
+          <t>526737</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
         <is>
-          <t>45,12%</t>
+          <t>45,72%</t>
         </is>
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>40,97%</t>
+          <t>42,23%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>48,33%</t>
+          <t>49,12%</t>
         </is>
       </c>
     </row>
@@ -10461,32 +10461,32 @@
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>176104</t>
+          <t>168702</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>146405</t>
+          <t>144607</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>195164</t>
+          <t>187206</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
         <is>
-          <t>73,22%</t>
+          <t>71,11%</t>
         </is>
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>60,87%</t>
+          <t>60,96%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>81,15%</t>
+          <t>78,91%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -10496,32 +10496,32 @@
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>368943</t>
+          <t>413382</t>
         </is>
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>342703</t>
+          <t>386653</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>393772</t>
+          <t>444379</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>49,02%</t>
+          <t>49,5%</t>
         </is>
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>45,53%</t>
+          <t>46,3%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>52,32%</t>
+          <t>53,21%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -10531,32 +10531,32 @@
       </c>
       <c r="R20" s="2" t="inlineStr">
         <is>
-          <t>545047</t>
+          <t>582083</t>
         </is>
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>513114</t>
+          <t>545675</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>586286</t>
+          <t>619493</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
         <is>
-          <t>54,88%</t>
+          <t>54,28%</t>
         </is>
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>51,67%</t>
+          <t>50,88%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>59,03%</t>
+          <t>57,77%</t>
         </is>
       </c>
     </row>
@@ -10574,17 +10574,17 @@
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>240507</t>
+          <t>237228</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>240507</t>
+          <t>237228</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>240507</t>
+          <t>237228</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -10609,17 +10609,17 @@
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>752620</t>
+          <t>835184</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>752620</t>
+          <t>835184</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>752620</t>
+          <t>835184</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -10644,17 +10644,17 @@
       </c>
       <c r="R21" s="2" t="inlineStr">
         <is>
-          <t>993127</t>
+          <t>1072412</t>
         </is>
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>993127</t>
+          <t>1072412</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>993127</t>
+          <t>1072412</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -10691,32 +10691,32 @@
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t>1288143</t>
+          <t>1425375</t>
         </is>
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>980323</t>
+          <t>1368436</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>1405243</t>
+          <t>1494974</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
         <is>
-          <t>38,33%</t>
+          <t>41,61%</t>
         </is>
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>29,17%</t>
+          <t>39,95%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>41,82%</t>
+          <t>43,64%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -10726,32 +10726,32 @@
       </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>1913125</t>
+          <t>1831128</t>
         </is>
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>1774767</t>
+          <t>1781540</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>2234950</t>
+          <t>1884849</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
         <is>
-          <t>53,75%</t>
+          <t>50,64%</t>
         </is>
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>49,86%</t>
+          <t>49,27%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>62,79%</t>
+          <t>52,13%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -10761,32 +10761,32 @@
       </c>
       <c r="R22" s="2" t="inlineStr">
         <is>
-          <t>3201268</t>
+          <t>3256503</t>
         </is>
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>2868149</t>
+          <t>3173568</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>3513583</t>
+          <t>3333723</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
         <is>
-          <t>46,26%</t>
+          <t>46,25%</t>
         </is>
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>41,45%</t>
+          <t>45,07%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>50,78%</t>
+          <t>47,35%</t>
         </is>
       </c>
     </row>
@@ -10804,32 +10804,32 @@
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>2072431</t>
+          <t>2000109</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>1955331</t>
+          <t>1930510</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>2380251</t>
+          <t>2057048</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>61,67%</t>
+          <t>58,39%</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>58,18%</t>
+          <t>56,36%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>70,83%</t>
+          <t>60,05%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -10839,32 +10839,32 @@
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>1646079</t>
+          <t>1784641</t>
         </is>
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>1324254</t>
+          <t>1730920</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>1784437</t>
+          <t>1834229</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
         <is>
-          <t>46,25%</t>
+          <t>49,36%</t>
         </is>
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>37,21%</t>
+          <t>47,87%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>50,14%</t>
+          <t>50,73%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -10874,32 +10874,32 @@
       </c>
       <c r="R23" s="2" t="inlineStr">
         <is>
-          <t>3718510</t>
+          <t>3784750</t>
         </is>
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>3406195</t>
+          <t>3707530</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>4051629</t>
+          <t>3867685</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
         <is>
-          <t>53,74%</t>
+          <t>53,75%</t>
         </is>
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>49,22%</t>
+          <t>52,65%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>58,55%</t>
+          <t>54,93%</t>
         </is>
       </c>
     </row>
@@ -10917,17 +10917,17 @@
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>3360574</t>
+          <t>3425484</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>3360574</t>
+          <t>3425484</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>3360574</t>
+          <t>3425484</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -10952,17 +10952,17 @@
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>3559204</t>
+          <t>3615769</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>3559204</t>
+          <t>3615769</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>3559204</t>
+          <t>3615769</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -10987,17 +10987,17 @@
       </c>
       <c r="R24" s="2" t="inlineStr">
         <is>
-          <t>6919778</t>
+          <t>7041253</t>
         </is>
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>6919778</t>
+          <t>7041253</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>6919778</t>
+          <t>7041253</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
